--- a/data/trans_orig/IQ19B_A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ19B_A-Habitat-trans_orig.xlsx
@@ -1326,7 +1326,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3300</t>
+          <t>3316</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>3253</t>
+          <t>3309</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3606</t>
+          <t>3093</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3543</t>
+          <t>3604</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3677</t>
+          <t>3736</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>3678</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4897</t>
+          <t>4277</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -1619,12 +1619,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>604</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4414</t>
+          <t>4531</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7625</t>
+          <t>7353</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1669,12 +1669,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2566</t>
+          <t>3071</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9539</t>
+          <t>10612</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>16,44%</t>
         </is>
       </c>
     </row>
@@ -1730,12 +1730,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1508</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8171</t>
+          <t>7846</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1765,12 +1765,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10667</t>
+          <t>10193</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1780,12 +1780,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1800,12 +1800,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6029</t>
+          <t>5712</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15681</t>
+          <t>15367</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1815,12 +1815,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>23,81%</t>
         </is>
       </c>
     </row>
@@ -1841,12 +1841,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11175</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18874</t>
+          <t>18642</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1856,12 +1856,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,52%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1876,12 +1876,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15260</t>
+          <t>15191</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25336</t>
+          <t>25456</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1891,12 +1891,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1911,12 +1911,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>28788</t>
+          <t>29036</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>41257</t>
+          <t>41935</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1926,12 +1926,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>64,98%</t>
         </is>
       </c>
     </row>
@@ -1952,12 +1952,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1678</t>
+          <t>1942</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7848</t>
+          <t>8339</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1967,12 +1967,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1987,12 +1987,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3185</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10697</t>
+          <t>11524</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2002,12 +2002,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6572</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>16107</t>
+          <t>16148</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2037,12 +2037,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,02%</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3512</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3507</t>
+          <t>4001</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4446</t>
+          <t>3367</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4104</t>
+          <t>3315</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -3068,12 +3068,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>671</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5938</t>
+          <t>5980</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3103,12 +3103,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7181</t>
+          <t>7195</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3138,12 +3138,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2701</t>
+          <t>2668</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10529</t>
+          <t>10613</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,7%</t>
         </is>
       </c>
     </row>
@@ -3179,12 +3179,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1838</t>
+          <t>1844</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8252</t>
+          <t>8087</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3194,12 +3194,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3214,12 +3214,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2723</t>
+          <t>2699</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9756</t>
+          <t>9859</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3229,12 +3229,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6293</t>
+          <t>6308</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>15646</t>
+          <t>15861</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,98%</t>
         </is>
       </c>
     </row>
@@ -3290,12 +3290,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>22896</t>
+          <t>22423</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>32643</t>
+          <t>32058</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>75,86%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>20268</t>
+          <t>20124</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>30097</t>
+          <t>29403</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3340,12 +3340,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>45743</t>
+          <t>45939</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>60053</t>
+          <t>60469</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3375,12 +3375,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>72,36%</t>
         </is>
       </c>
     </row>
@@ -3401,12 +3401,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4133</t>
+          <t>4207</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>11871</t>
+          <t>11806</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2697</t>
+          <t>2709</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>9546</t>
+          <t>10077</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3471,12 +3471,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7777</t>
+          <t>8966</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>18800</t>
+          <t>18898</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,61%</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1981</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>2967</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -4522,7 +4522,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2842</t>
+          <t>3285</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4557,7 +4557,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>4260</t>
+          <t>4148</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4587,12 +4587,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>467</t>
+          <t>460</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>5147</t>
+          <t>5025</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4602,12 +4602,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -4628,12 +4628,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>2695</t>
+          <t>2585</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>9412</t>
+          <t>8814</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>2456</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>9278</t>
+          <t>8903</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>6288</t>
+          <t>6078</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>15297</t>
+          <t>15362</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4713,12 +4713,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,4%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>14670</t>
+          <t>14805</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>23018</t>
+          <t>23223</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>17853</t>
+          <t>17714</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>26100</t>
+          <t>26401</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>35243</t>
+          <t>35417</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>46919</t>
+          <t>47280</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>53,96%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>72,03%</t>
         </is>
       </c>
     </row>
@@ -4850,12 +4850,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>3894</t>
+          <t>3862</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>10781</t>
+          <t>11048</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4865,12 +4865,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>2215</t>
+          <t>1983</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>8814</t>
+          <t>8366</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4920,12 +4920,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>7238</t>
+          <t>7559</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>16528</t>
+          <t>16806</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -4935,12 +4935,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,6%</t>
         </is>
       </c>
     </row>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3634</t>
+          <t>3740</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3288</t>
+          <t>3292</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -5860,7 +5860,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>4448</t>
+          <t>5052</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>5035</t>
+          <t>4926</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -5945,7 +5945,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>2649</t>
+          <t>3302</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6021,7 +6021,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>3762</t>
+          <t>3626</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6056,7 +6056,7 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>2187</t>
+          <t>2246</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>9249</t>
+          <t>9824</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>6948</t>
+          <t>7517</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>4823</t>
+          <t>4877</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>14207</t>
+          <t>14010</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,14%</t>
         </is>
       </c>
     </row>
@@ -6188,12 +6188,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>12907</t>
+          <t>13314</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>22725</t>
+          <t>22713</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>19967</t>
+          <t>20556</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>29133</t>
+          <t>29795</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>37269</t>
+          <t>36359</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>49665</t>
+          <t>49867</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>54,85%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>75,23%</t>
         </is>
       </c>
     </row>
@@ -6299,12 +6299,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>2253</t>
+          <t>2402</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>10613</t>
+          <t>9952</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>3382</t>
+          <t>3365</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>11034</t>
+          <t>10864</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>6746</t>
+          <t>7131</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>16644</t>
+          <t>17401</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>26,25%</t>
         </is>
       </c>
     </row>
@@ -6678,7 +6678,7 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>3212</t>
+          <t>3242</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6693,7 +6693,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6713,7 +6713,7 @@
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3233</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>4712</t>
+          <t>4776</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>4166</t>
+          <t>4813</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7172,7 +7172,7 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -7233,7 +7233,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>4252</t>
+          <t>4798</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7268,7 +7268,7 @@
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>4219</t>
+          <t>4767</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7283,7 +7283,7 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -7309,7 +7309,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>6259</t>
+          <t>5870</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>4132</t>
+          <t>4178</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7359,7 +7359,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>731</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>7768</t>
+          <t>6787</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -7415,12 +7415,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>2541</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>9895</t>
+          <t>10084</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7430,12 +7430,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7450,12 +7450,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>5030</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>14401</t>
+          <t>13949</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -7465,12 +7465,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7485,12 +7485,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>9402</t>
+          <t>9245</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>21163</t>
+          <t>20625</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -7526,12 +7526,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>13385</t>
+          <t>12697</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>26104</t>
+          <t>26303</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>14265</t>
+          <t>14566</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>28323</t>
+          <t>27843</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>31274</t>
+          <t>31680</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>49469</t>
+          <t>50886</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -7611,12 +7611,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>18,17%</t>
         </is>
       </c>
     </row>
@@ -7637,12 +7637,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>70195</t>
+          <t>70293</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>88083</t>
+          <t>87670</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>54,23%</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -7672,12 +7672,12 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>83628</t>
+          <t>84313</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>103253</t>
+          <t>102853</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>159535</t>
+          <t>159202</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>184425</t>
+          <t>184346</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>65,83%</t>
         </is>
       </c>
     </row>
@@ -7748,12 +7748,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>16873</t>
+          <t>17741</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>31392</t>
+          <t>31521</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>16962</t>
+          <t>16423</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>31496</t>
+          <t>30604</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -7798,12 +7798,12 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -7818,12 +7818,12 @@
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>37235</t>
+          <t>37834</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>57477</t>
+          <t>56584</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -7833,12 +7833,12 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,21%</t>
         </is>
       </c>
     </row>
@@ -8359,7 +8359,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3798</t>
+          <t>3341</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8394,7 +8394,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3479</t>
+          <t>3918</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3638</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8561,7 +8561,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t>3730</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -8768,7 +8768,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>6234</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8783,7 +8783,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8838,7 +8838,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7657</t>
+          <t>7235</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8853,7 +8853,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>11,98%</t>
         </is>
       </c>
     </row>
@@ -8990,7 +8990,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5764</t>
+          <t>5531</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9005,7 +9005,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9060,7 +9060,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5177</t>
+          <t>5205</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9075,7 +9075,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -9101,7 +9101,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3522</t>
+          <t>4080</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3935</t>
+          <t>4220</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9186,7 +9186,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1584</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8516</t>
+          <t>8485</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>626</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5181</t>
+          <t>4734</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3171</t>
+          <t>2992</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11247</t>
+          <t>11383</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,84%</t>
         </is>
       </c>
     </row>
@@ -9318,12 +9318,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15012</t>
+          <t>14554</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24880</t>
+          <t>24512</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9353,12 +9353,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16827</t>
+          <t>16441</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23608</t>
+          <t>23562</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9368,12 +9368,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9388,12 +9388,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>34440</t>
+          <t>34417</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>46378</t>
+          <t>46050</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9403,12 +9403,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>56,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,23%</t>
         </is>
       </c>
     </row>
@@ -9429,12 +9429,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2736</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9892</t>
+          <t>9323</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9464,12 +9464,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>775</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6008</t>
+          <t>6931</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9499,12 +9499,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4872</t>
+          <t>4873</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>13953</t>
+          <t>13567</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9514,12 +9514,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>22,46%</t>
         </is>
       </c>
     </row>
@@ -9808,7 +9808,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3243</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9823,7 +9823,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9843,7 +9843,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3565</t>
+          <t>3285</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9858,7 +9858,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3659</t>
+          <t>3067</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10232,7 +10232,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10287,7 +10287,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3068</t>
+          <t>3071</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>648</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5871</t>
+          <t>6431</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10393,12 +10393,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>646</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6351</t>
+          <t>6317</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10413,7 +10413,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -10439,7 +10439,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5376</t>
+          <t>5427</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10454,7 +10454,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10509,7 +10509,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4849</t>
+          <t>5164</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10524,7 +10524,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -10550,7 +10550,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3945</t>
+          <t>3694</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10565,7 +10565,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10580,12 +10580,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>1327</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7095</t>
+          <t>7528</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10595,12 +10595,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10615,12 +10615,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>1436</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8237</t>
+          <t>8242</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10630,12 +10630,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -10656,12 +10656,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3757</t>
+          <t>3639</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>11355</t>
+          <t>11491</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10671,12 +10671,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10691,12 +10691,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>2497</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9191</t>
+          <t>9380</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10706,12 +10706,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10726,12 +10726,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>7337</t>
+          <t>6471</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>17245</t>
+          <t>17133</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10741,12 +10741,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,19%</t>
         </is>
       </c>
     </row>
@@ -10767,12 +10767,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>22959</t>
+          <t>23018</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>32449</t>
+          <t>32801</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10782,12 +10782,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -10802,12 +10802,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>26642</t>
+          <t>27145</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>38356</t>
+          <t>38165</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10817,12 +10817,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -10837,12 +10837,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>53114</t>
+          <t>52795</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>68001</t>
+          <t>67837</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10852,12 +10852,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>72,01%</t>
         </is>
       </c>
     </row>
@@ -10878,12 +10878,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2544</t>
+          <t>2495</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>9878</t>
+          <t>9721</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10913,12 +10913,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3907</t>
+          <t>3902</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>12095</t>
+          <t>11698</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10948,12 +10948,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7793</t>
+          <t>8256</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>18658</t>
+          <t>19032</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>20,2%</t>
         </is>
       </c>
     </row>
@@ -11444,7 +11444,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11459,7 +11459,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11514,7 +11514,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -11701,7 +11701,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>1790</t>
+          <t>1807</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -11716,7 +11716,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -11736,7 +11736,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>2047</t>
+          <t>2209</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -11751,7 +11751,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>5581</t>
+          <t>5980</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -12014,7 +12014,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -12029,12 +12029,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>596</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>4378</t>
+          <t>4885</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -12049,7 +12049,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -12064,12 +12064,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1586</t>
+          <t>1602</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>8148</t>
+          <t>8408</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -12079,12 +12079,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>14,3%</t>
         </is>
       </c>
     </row>
@@ -12105,12 +12105,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>1589</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>7386</t>
+          <t>7735</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -12120,12 +12120,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -12140,12 +12140,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>5980</t>
+          <t>6075</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -12155,12 +12155,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -12175,12 +12175,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>3368</t>
+          <t>3465</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>10820</t>
+          <t>10738</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -12190,12 +12190,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,26%</t>
         </is>
       </c>
     </row>
@@ -12216,12 +12216,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>13697</t>
+          <t>13194</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>22187</t>
+          <t>21736</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -12231,12 +12231,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -12251,12 +12251,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>17868</t>
+          <t>17825</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>25254</t>
+          <t>25467</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -12266,12 +12266,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>59,17%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -12286,12 +12286,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>34704</t>
+          <t>34150</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>46039</t>
+          <t>45717</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -12301,12 +12301,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>58,07%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>77,73%</t>
         </is>
       </c>
     </row>
@@ -12327,12 +12327,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1392</t>
+          <t>1648</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>8136</t>
+          <t>8533</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -12342,12 +12342,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -12362,12 +12362,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>1173</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>6658</t>
+          <t>6497</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -12377,12 +12377,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -12397,12 +12397,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>3853</t>
+          <t>3734</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>12200</t>
+          <t>12066</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -12412,12 +12412,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,52%</t>
         </is>
       </c>
     </row>
@@ -12928,7 +12928,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>2721</t>
+          <t>3370</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -12943,7 +12943,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -12963,7 +12963,7 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>3250</t>
+          <t>2978</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -12978,7 +12978,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -13004,7 +13004,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>4702</t>
+          <t>4572</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -13019,7 +13019,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -13074,7 +13074,7 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>4648</t>
+          <t>4615</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -13089,7 +13089,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -13372,7 +13372,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>4358</t>
+          <t>4150</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -13387,7 +13387,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>3979</t>
+          <t>4622</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -13422,7 +13422,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -13443,12 +13443,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>722</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>6657</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -13458,12 +13458,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -13478,12 +13478,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>605</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>5132</t>
+          <t>5345</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -13493,12 +13493,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -13513,12 +13513,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>2159</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>9292</t>
+          <t>10099</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -13528,12 +13528,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>13,38%</t>
         </is>
       </c>
     </row>
@@ -13554,12 +13554,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>3375</t>
+          <t>3394</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>10966</t>
+          <t>11151</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -13569,12 +13569,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -13589,12 +13589,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>9251</t>
+          <t>9320</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>6771</t>
+          <t>6997</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>17168</t>
+          <t>17194</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,78%</t>
         </is>
       </c>
     </row>
@@ -13665,12 +13665,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>11683</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>21670</t>
+          <t>20985</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -13680,12 +13680,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -13700,12 +13700,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>18423</t>
+          <t>18610</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>30184</t>
+          <t>29389</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -13715,12 +13715,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -13735,12 +13735,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>32948</t>
+          <t>33738</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>47495</t>
+          <t>48612</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -13750,12 +13750,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>64,4%</t>
         </is>
       </c>
     </row>
@@ -13776,12 +13776,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>10021</t>
+          <t>10527</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -13791,12 +13791,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -13811,12 +13811,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>5703</t>
+          <t>5706</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>15708</t>
+          <t>15124</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -13826,12 +13826,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -13846,12 +13846,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>9881</t>
+          <t>9258</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>22266</t>
+          <t>22219</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -13861,12 +13861,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,44%</t>
         </is>
       </c>
     </row>
@@ -14155,7 +14155,7 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>4085</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -14170,7 +14170,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -14190,7 +14190,7 @@
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>4693</t>
+          <t>4750</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -14205,7 +14205,7 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -14342,7 +14342,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>4339</t>
+          <t>4714</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -14357,7 +14357,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -14377,7 +14377,7 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2633</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -14392,7 +14392,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -14407,12 +14407,12 @@
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>463</t>
+          <t>464</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>5112</t>
+          <t>4819</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -14453,7 +14453,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>4606</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -14523,7 +14523,7 @@
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>4685</t>
+          <t>5366</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -14538,7 +14538,7 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -14564,7 +14564,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>7406</t>
+          <t>6806</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -14579,7 +14579,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -14599,7 +14599,7 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>2180</t>
+          <t>2164</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -14614,7 +14614,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -14629,12 +14629,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>435</t>
+          <t>430</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>7982</t>
+          <t>7337</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -14649,7 +14649,7 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -14705,12 +14705,12 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>728</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>6365</t>
+          <t>7418</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -14725,7 +14725,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -14740,12 +14740,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>653</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>5936</t>
+          <t>7336</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -14755,12 +14755,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -14781,12 +14781,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>861</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>7286</t>
+          <t>7513</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -14801,7 +14801,7 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -14821,7 +14821,7 @@
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>4776</t>
+          <t>4428</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -14836,7 +14836,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -14851,12 +14851,12 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>1942</t>
+          <t>1582</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>10030</t>
+          <t>9091</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -14866,12 +14866,12 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -14892,12 +14892,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>3144</t>
+          <t>3014</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>12181</t>
+          <t>11876</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -14907,12 +14907,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -14927,12 +14927,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>3825</t>
+          <t>3889</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>12225</t>
+          <t>12519</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -14942,12 +14942,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>8740</t>
+          <t>8568</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>21008</t>
+          <t>20643</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -14977,12 +14977,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>15012</t>
+          <t>15196</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>28956</t>
+          <t>28816</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -15018,12 +15018,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>9393</t>
+          <t>9246</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>21031</t>
+          <t>20751</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -15053,12 +15053,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -15073,12 +15073,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>27090</t>
+          <t>26575</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>45055</t>
+          <t>45398</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -15088,12 +15088,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,71%</t>
         </is>
       </c>
     </row>
@@ -15114,12 +15114,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>73158</t>
+          <t>72736</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>91704</t>
+          <t>91961</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -15129,12 +15129,12 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -15149,12 +15149,12 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>91416</t>
+          <t>90049</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>109993</t>
+          <t>109756</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -15164,12 +15164,12 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -15184,12 +15184,12 @@
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>169937</t>
+          <t>168769</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>197016</t>
+          <t>195874</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
@@ -15199,12 +15199,12 @@
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>67,8%</t>
         </is>
       </c>
     </row>
@@ -15225,12 +15225,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>14081</t>
+          <t>13940</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>27858</t>
+          <t>28848</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -15240,12 +15240,12 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -15260,12 +15260,12 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>16485</t>
+          <t>15893</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>31148</t>
+          <t>31187</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -15275,12 +15275,12 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -15295,12 +15295,12 @@
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>34601</t>
+          <t>33871</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>54624</t>
+          <t>54409</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -15310,12 +15310,12 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,83%</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3046</t>
+          <t>2808</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -16149,7 +16149,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -16204,7 +16204,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3065</t>
+          <t>3011</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -16219,7 +16219,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -16502,7 +16502,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6133</t>
+          <t>6318</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -16517,7 +16517,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -16537,7 +16537,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7115</t>
+          <t>5967</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -16552,7 +16552,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>9,61%</t>
         </is>
       </c>
     </row>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3375</t>
+          <t>3593</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -16593,7 +16593,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -16613,7 +16613,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4828</t>
+          <t>5431</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -16628,7 +16628,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -16643,12 +16643,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>670</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5908</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -16663,7 +16663,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -16684,12 +16684,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>643</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6482</t>
+          <t>6455</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -16699,12 +16699,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -16719,12 +16719,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3426</t>
+          <t>3369</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11572</t>
+          <t>11726</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -16734,12 +16734,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -16754,12 +16754,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4721</t>
+          <t>4792</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14981</t>
+          <t>15193</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -16769,12 +16769,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,47%</t>
         </is>
       </c>
     </row>
@@ -16795,12 +16795,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16331</t>
+          <t>16451</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25205</t>
+          <t>25131</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -16810,12 +16810,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -16830,12 +16830,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13785</t>
+          <t>14005</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23377</t>
+          <t>23728</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -16845,12 +16845,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,3%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -16865,12 +16865,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>33027</t>
+          <t>32907</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>46583</t>
+          <t>45945</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -16880,12 +16880,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>53,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>74,01%</t>
         </is>
       </c>
     </row>
@@ -16906,12 +16906,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2293</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8989</t>
+          <t>10161</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -16921,12 +16921,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -16941,12 +16941,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>748</t>
+          <t>740</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6910</t>
+          <t>6812</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -16956,12 +16956,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -16976,12 +16976,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4362</t>
+          <t>4321</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>13549</t>
+          <t>13674</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -16991,12 +16991,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>22,03%</t>
         </is>
       </c>
     </row>
@@ -18027,7 +18027,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4312</t>
+          <t>3924</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -18042,7 +18042,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -18097,7 +18097,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3831</t>
+          <t>3797</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -18112,7 +18112,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -18133,12 +18133,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5004</t>
+          <t>5366</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13955</t>
+          <t>13952</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -18148,12 +18148,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -18168,12 +18168,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2529</t>
+          <t>2542</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9475</t>
+          <t>9634</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -18183,12 +18183,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -18203,12 +18203,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>8884</t>
+          <t>9269</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>20076</t>
+          <t>20276</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -18218,12 +18218,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,58%</t>
         </is>
       </c>
     </row>
@@ -18244,12 +18244,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>21009</t>
+          <t>20937</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>31296</t>
+          <t>31431</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -18259,12 +18259,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,93%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -18279,12 +18279,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>27172</t>
+          <t>27466</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>36372</t>
+          <t>36445</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -18294,12 +18294,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>64,05%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -18314,12 +18314,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>51710</t>
+          <t>51980</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>65659</t>
+          <t>65999</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -18329,12 +18329,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>76,76%</t>
         </is>
       </c>
     </row>
@@ -18355,12 +18355,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>3160</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>10881</t>
+          <t>10669</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -18390,12 +18390,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2543</t>
+          <t>2544</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>9582</t>
+          <t>9019</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -18410,7 +18410,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -18425,12 +18425,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7226</t>
+          <t>7652</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>17961</t>
+          <t>17536</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -18440,12 +18440,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,39%</t>
         </is>
       </c>
     </row>
@@ -19067,7 +19067,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2879</t>
+          <t>3155</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -19082,7 +19082,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -19102,7 +19102,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3851</t>
+          <t>2975</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -19117,7 +19117,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -19365,7 +19365,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3983</t>
+          <t>3232</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -19380,7 +19380,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -19435,7 +19435,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3743</t>
+          <t>3827</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -19450,7 +19450,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -19511,7 +19511,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>4142</t>
+          <t>4137</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -19526,7 +19526,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -19546,7 +19546,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>4253</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -19561,7 +19561,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -19582,12 +19582,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>671</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>6418</t>
+          <t>6059</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -19597,12 +19597,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -19617,12 +19617,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>3387</t>
+          <t>3259</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>10778</t>
+          <t>10530</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -19632,12 +19632,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -19652,12 +19652,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>5749</t>
+          <t>5147</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>14833</t>
+          <t>15086</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -19667,12 +19667,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,43%</t>
         </is>
       </c>
     </row>
@@ -19693,12 +19693,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>17985</t>
+          <t>18230</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>26312</t>
+          <t>25721</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -19708,12 +19708,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -19728,12 +19728,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>11852</t>
+          <t>12008</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>21016</t>
+          <t>20905</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -19743,12 +19743,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>67,96%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -19763,12 +19763,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>32023</t>
+          <t>32712</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>44692</t>
+          <t>45181</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -19778,12 +19778,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>52,97%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>73,16%</t>
         </is>
       </c>
     </row>
@@ -19804,12 +19804,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>2432</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>9290</t>
+          <t>8692</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -19819,12 +19819,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -19839,12 +19839,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>2614</t>
+          <t>2338</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>10520</t>
+          <t>10591</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -19854,12 +19854,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -19874,12 +19874,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>6472</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>16598</t>
+          <t>16810</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -19889,12 +19889,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>27,22%</t>
         </is>
       </c>
     </row>
@@ -20703,7 +20703,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>3723</t>
+          <t>3744</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -20718,7 +20718,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -20738,7 +20738,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>4044</t>
+          <t>3186</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -20753,7 +20753,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -20773,7 +20773,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>4565</t>
+          <t>4753</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -20788,7 +20788,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -20849,7 +20849,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>4885</t>
+          <t>4377</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -20864,7 +20864,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -20884,7 +20884,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>4807</t>
+          <t>4940</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -20899,7 +20899,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -20925,7 +20925,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>4534</t>
+          <t>4911</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -20940,7 +20940,7 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -20960,7 +20960,7 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>4389</t>
+          <t>4255</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -20975,7 +20975,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -20990,12 +20990,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>634</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>5894</t>
+          <t>5912</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -21010,7 +21010,7 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -21031,12 +21031,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>2387</t>
+          <t>2380</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>10377</t>
+          <t>10332</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -21046,12 +21046,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -21066,12 +21066,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>1830</t>
+          <t>1864</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>9756</t>
+          <t>9314</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -21081,12 +21081,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>5276</t>
+          <t>5496</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>16024</t>
+          <t>16607</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -21116,12 +21116,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>16,0%</t>
         </is>
       </c>
     </row>
@@ -21142,12 +21142,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>22976</t>
+          <t>22611</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>35058</t>
+          <t>34382</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -21157,12 +21157,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>47,11%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -21177,12 +21177,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>29063</t>
+          <t>29994</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>41421</t>
+          <t>41675</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -21192,12 +21192,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -21212,12 +21212,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>55422</t>
+          <t>56231</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>72889</t>
+          <t>73166</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -21227,12 +21227,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>70,5%</t>
         </is>
       </c>
     </row>
@@ -21253,12 +21253,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>6743</t>
+          <t>7126</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>16846</t>
+          <t>17875</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -21268,12 +21268,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -21288,12 +21288,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>8204</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>18874</t>
+          <t>18823</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -21303,12 +21303,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -21323,12 +21323,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>17778</t>
+          <t>17169</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>32622</t>
+          <t>32515</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -21338,12 +21338,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,33%</t>
         </is>
       </c>
     </row>
@@ -21930,7 +21930,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>2983</t>
+          <t>3319</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -21945,7 +21945,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -21965,7 +21965,7 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>3952</t>
+          <t>3233</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -21980,7 +21980,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -22000,7 +22000,7 @@
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>4126</t>
+          <t>4605</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -22015,7 +22015,7 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -22152,7 +22152,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>4166</t>
+          <t>3380</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -22167,7 +22167,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -22187,7 +22187,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>2675</t>
+          <t>3793</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -22202,7 +22202,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -22222,7 +22222,7 @@
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>4430</t>
+          <t>4625</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -22237,7 +22237,7 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -22263,7 +22263,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>4606</t>
+          <t>4573</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -22278,7 +22278,7 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -22293,12 +22293,12 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>728</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>8218</t>
+          <t>7931</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -22308,12 +22308,12 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -22328,12 +22328,12 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>1418</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>8976</t>
+          <t>8688</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -22343,12 +22343,12 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -22369,12 +22369,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1209</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>7096</t>
+          <t>7493</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -22384,12 +22384,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -22404,12 +22404,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>1352</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>7690</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -22419,12 +22419,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -22439,12 +22439,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>3586</t>
+          <t>3513</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>12629</t>
+          <t>11895</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -22454,12 +22454,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -22480,12 +22480,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>13374</t>
+          <t>13442</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>27626</t>
+          <t>26913</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -22495,12 +22495,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -22515,12 +22515,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>16438</t>
+          <t>16239</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>32327</t>
+          <t>30968</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -22530,12 +22530,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -22550,12 +22550,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>33083</t>
+          <t>32800</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>52933</t>
+          <t>53517</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -22565,12 +22565,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,06%</t>
         </is>
       </c>
     </row>
@@ -22591,12 +22591,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>89325</t>
+          <t>89560</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>109473</t>
+          <t>108849</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -22606,12 +22606,12 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>58,81%</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -22626,12 +22626,12 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>92716</t>
+          <t>92387</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>113008</t>
+          <t>113344</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -22641,12 +22641,12 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>57,27%</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>70,26%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -22661,12 +22661,12 @@
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>187732</t>
+          <t>188300</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>216330</t>
+          <t>217145</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
@@ -22676,12 +22676,12 @@
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>69,24%</t>
         </is>
       </c>
     </row>
@@ -22702,12 +22702,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>20835</t>
+          <t>20063</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>36283</t>
+          <t>36083</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -22717,12 +22717,12 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -22737,12 +22737,12 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>19239</t>
+          <t>19272</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>36048</t>
+          <t>34960</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -22752,12 +22752,12 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -22772,12 +22772,12 @@
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>44720</t>
+          <t>44067</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>67044</t>
+          <t>66458</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -22787,12 +22787,12 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,19%</t>
         </is>
       </c>
     </row>
@@ -23424,7 +23424,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5556</t>
+          <t>5796</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -23439,7 +23439,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -23459,7 +23459,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5611</t>
+          <t>5011</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -23474,7 +23474,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -24055,7 +24055,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>2304</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -24070,7 +24070,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -24125,7 +24125,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3172</t>
+          <t>2667</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -24140,7 +24140,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -24161,12 +24161,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2394</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9256</t>
+          <t>9238</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -24176,12 +24176,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -24196,12 +24196,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3088</t>
+          <t>3228</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11825</t>
+          <t>12378</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -24211,12 +24211,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -24231,12 +24231,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7090</t>
+          <t>6611</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17556</t>
+          <t>18342</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -24246,12 +24246,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>23,13%</t>
         </is>
       </c>
     </row>
@@ -24272,12 +24272,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11507</t>
+          <t>11211</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21157</t>
+          <t>21044</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -24287,12 +24287,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -24307,12 +24307,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18891</t>
+          <t>18516</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>31676</t>
+          <t>31149</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -24322,12 +24322,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>70,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -24342,12 +24342,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>33516</t>
+          <t>33720</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>49388</t>
+          <t>49899</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -24357,12 +24357,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>62,93%</t>
         </is>
       </c>
     </row>
@@ -24383,12 +24383,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9132</t>
+          <t>8675</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17956</t>
+          <t>17868</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -24398,12 +24398,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>50,96%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -24418,12 +24418,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5445</t>
+          <t>6248</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17221</t>
+          <t>18524</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -24433,12 +24433,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -24453,12 +24453,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>17330</t>
+          <t>16764</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>32049</t>
+          <t>32227</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -24468,12 +24468,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,65%</t>
         </is>
       </c>
     </row>
@@ -25206,7 +25206,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4515</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -25221,7 +25221,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -25241,7 +25241,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4023</t>
+          <t>4016</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -25499,12 +25499,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>775</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6445</t>
+          <t>6371</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -25514,12 +25514,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -25539,7 +25539,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7370</t>
+          <t>6918</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -25554,7 +25554,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -25569,12 +25569,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1801</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10796</t>
+          <t>10475</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -25584,12 +25584,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -25610,12 +25610,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4548</t>
+          <t>4648</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>14131</t>
+          <t>14489</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -25625,12 +25625,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -25645,12 +25645,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10505</t>
+          <t>10777</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>23592</t>
+          <t>24307</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -25660,12 +25660,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -25680,12 +25680,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>17413</t>
+          <t>17228</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>34685</t>
+          <t>34198</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -25695,12 +25695,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,61%</t>
         </is>
       </c>
     </row>
@@ -25721,12 +25721,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>25835</t>
+          <t>25334</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>38915</t>
+          <t>39118</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -25736,12 +25736,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -25756,12 +25756,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>44966</t>
+          <t>46068</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>62373</t>
+          <t>63154</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -25771,12 +25771,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>52,19%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -25791,12 +25791,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>74740</t>
+          <t>76035</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>97863</t>
+          <t>96677</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -25806,12 +25806,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>63,92%</t>
         </is>
       </c>
     </row>
@@ -25832,12 +25832,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>14221</t>
+          <t>14017</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>27080</t>
+          <t>26005</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -25847,12 +25847,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -25867,12 +25867,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>9333</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>23208</t>
+          <t>23254</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -25882,12 +25882,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -25902,12 +25902,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>26303</t>
+          <t>26963</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>44259</t>
+          <t>44755</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -25917,12 +25917,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,59%</t>
         </is>
       </c>
     </row>
@@ -26731,7 +26731,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4659</t>
+          <t>3419</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -26746,7 +26746,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -26766,7 +26766,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>6712</t>
+          <t>7625</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -26781,7 +26781,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -26801,7 +26801,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>9299</t>
+          <t>9179</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -26816,7 +26816,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -26953,7 +26953,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>4555</t>
+          <t>4570</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -26968,7 +26968,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -27023,7 +27023,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>5133</t>
+          <t>3654</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -27038,7 +27038,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -27059,12 +27059,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>2794</t>
+          <t>2778</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>11192</t>
+          <t>10708</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -27074,12 +27074,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -27094,12 +27094,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>3101</t>
+          <t>3428</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>13115</t>
+          <t>13800</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -27109,12 +27109,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -27129,12 +27129,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>7503</t>
+          <t>7731</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>20433</t>
+          <t>20582</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -27144,12 +27144,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,35%</t>
         </is>
       </c>
     </row>
@@ -27170,12 +27170,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>24546</t>
+          <t>24501</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>39153</t>
+          <t>39071</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -27185,12 +27185,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -27205,12 +27205,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>17457</t>
+          <t>16272</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>32786</t>
+          <t>32921</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -27220,12 +27220,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -27240,12 +27240,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>47348</t>
+          <t>46132</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>69571</t>
+          <t>69495</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -27255,12 +27255,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>62,02%</t>
+          <t>61,95%</t>
         </is>
       </c>
     </row>
@@ -27281,12 +27281,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>8248</t>
+          <t>7828</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>22646</t>
+          <t>21599</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -27296,12 +27296,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -27316,12 +27316,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>16779</t>
+          <t>17053</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>33338</t>
+          <t>33693</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -27331,12 +27331,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>57,81%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -27351,12 +27351,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>27935</t>
+          <t>28550</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>50073</t>
+          <t>51010</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -27366,12 +27366,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>45,47%</t>
         </is>
       </c>
     </row>
@@ -27514,7 +27514,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3928</t>
+          <t>3636</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -27529,7 +27529,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -27549,7 +27549,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>6560</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -27564,7 +27564,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -27584,7 +27584,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>6740</t>
+          <t>6430</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -27599,7 +27599,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -27736,7 +27736,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>3703</t>
+          <t>3194</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -27751,7 +27751,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -27806,7 +27806,7 @@
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>3185</t>
+          <t>3215</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -27821,7 +27821,7 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -27958,7 +27958,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>4604</t>
+          <t>3671</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -27973,7 +27973,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -27993,7 +27993,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>5621</t>
+          <t>3981</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -28008,7 +28008,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -28028,7 +28028,7 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>5481</t>
+          <t>5893</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -28043,7 +28043,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -28180,7 +28180,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>4184</t>
+          <t>4349</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -28195,7 +28195,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -28250,7 +28250,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>3915</t>
+          <t>4308</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -28265,7 +28265,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -28326,7 +28326,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>3634</t>
+          <t>4631</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -28341,7 +28341,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -28361,7 +28361,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>3579</t>
+          <t>3743</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -28376,7 +28376,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -28402,7 +28402,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>3893</t>
+          <t>4879</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -28417,7 +28417,7 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -28437,7 +28437,7 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>7360</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -28452,7 +28452,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -28467,12 +28467,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>798</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>9499</t>
+          <t>8556</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -28487,7 +28487,7 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>9,35%</t>
         </is>
       </c>
     </row>
@@ -28508,12 +28508,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>9180</t>
+          <t>8541</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -28523,12 +28523,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -28543,12 +28543,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>2735</t>
+          <t>2752</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>11148</t>
+          <t>10621</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -28558,12 +28558,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -28578,12 +28578,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>6137</t>
+          <t>6010</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>16501</t>
+          <t>15871</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -28593,12 +28593,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,35%</t>
         </is>
       </c>
     </row>
@@ -28619,12 +28619,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>17801</t>
+          <t>17458</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>28808</t>
+          <t>28194</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -28634,12 +28634,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -28654,12 +28654,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>18705</t>
+          <t>20444</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>32890</t>
+          <t>33043</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -28669,12 +28669,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -28689,12 +28689,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>40632</t>
+          <t>42354</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>57742</t>
+          <t>59361</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -28704,12 +28704,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>64,89%</t>
         </is>
       </c>
     </row>
@@ -28730,12 +28730,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>6705</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>15915</t>
+          <t>16510</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -28745,12 +28745,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -28765,12 +28765,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>6749</t>
+          <t>7348</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>17552</t>
+          <t>17426</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -28780,12 +28780,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -28800,12 +28800,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>15417</t>
+          <t>15438</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>30100</t>
+          <t>29300</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -28815,12 +28815,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,03%</t>
         </is>
       </c>
     </row>
@@ -28963,7 +28963,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>4465</t>
+          <t>4459</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -28998,7 +28998,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>6091</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -29013,7 +29013,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -29033,7 +29033,7 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>6340</t>
+          <t>6188</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -29048,7 +29048,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -29185,7 +29185,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>3649</t>
+          <t>3488</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -29200,7 +29200,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -29220,7 +29220,7 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>5687</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -29235,7 +29235,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -29255,7 +29255,7 @@
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>5824</t>
+          <t>7399</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -29270,7 +29270,7 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -29407,7 +29407,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>3849</t>
+          <t>4009</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -29422,44 +29422,44 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>955</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>4740</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
           <t>1,98%</t>
         </is>
       </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>955</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr">
-        <is>
-          <t>5261</t>
-        </is>
-      </c>
-      <c r="N60" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="O60" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P60" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
           <t>2</t>
@@ -29477,7 +29477,7 @@
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -29492,7 +29492,7 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -29553,7 +29553,7 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>3345</t>
+          <t>3572</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -29568,7 +29568,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -29588,7 +29588,7 @@
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>3290</t>
+          <t>4379</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -29603,7 +29603,7 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -29629,7 +29629,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>4494</t>
+          <t>4959</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -29644,7 +29644,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -29664,7 +29664,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>8591</t>
+          <t>7451</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -29679,7 +29679,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -29694,12 +29694,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>727</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>8879</t>
+          <t>9329</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -29709,12 +29709,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -29775,7 +29775,7 @@
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>4445</t>
+          <t>3428</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -29790,7 +29790,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -29810,7 +29810,7 @@
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>3920</t>
+          <t>3378</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -29825,7 +29825,7 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -29846,12 +29846,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2257</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>9476</t>
+          <t>9510</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -29861,12 +29861,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -29881,12 +29881,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>1749</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>10797</t>
+          <t>10216</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -29896,12 +29896,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -29916,12 +29916,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>4766</t>
+          <t>4774</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>16439</t>
+          <t>16478</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -29936,7 +29936,7 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -29957,12 +29957,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>17252</t>
+          <t>18200</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>32707</t>
+          <t>33198</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -29972,12 +29972,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -29992,12 +29992,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>26712</t>
+          <t>26907</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>46372</t>
+          <t>45898</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -30007,12 +30007,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -30027,12 +30027,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>48095</t>
+          <t>48014</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>74192</t>
+          <t>73042</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -30042,12 +30042,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,82%</t>
         </is>
       </c>
     </row>
@@ -30068,12 +30068,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>91543</t>
+          <t>90212</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>117446</t>
+          <t>115740</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -30083,49 +30083,49 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
+          <t>59,6%</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>131210</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>115297</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>145121</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>54,68%</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>48,05%</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
           <t>60,47%</t>
         </is>
       </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>131210</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="inlineStr">
-        <is>
-          <t>115413</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr">
-        <is>
-          <t>144540</t>
-        </is>
-      </c>
-      <c r="N66" s="2" t="inlineStr">
-        <is>
-          <t>54,68%</t>
-        </is>
-      </c>
-      <c r="O66" s="2" t="inlineStr">
-        <is>
-          <t>48,09%</t>
-        </is>
-      </c>
-      <c r="P66" s="2" t="inlineStr">
-        <is>
-          <t>60,23%</t>
-        </is>
-      </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
           <t>296</t>
@@ -30138,12 +30138,12 @@
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>216694</t>
+          <t>215412</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>256476</t>
+          <t>255025</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
@@ -30153,12 +30153,12 @@
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>58,74%</t>
         </is>
       </c>
     </row>
@@ -30179,12 +30179,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>46828</t>
+          <t>47277</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>69617</t>
+          <t>69162</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -30194,12 +30194,12 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -30214,12 +30214,12 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>49660</t>
+          <t>49888</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>77926</t>
+          <t>78583</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -30229,12 +30229,12 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -30249,12 +30249,12 @@
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>102770</t>
+          <t>102820</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>139082</t>
+          <t>139339</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -30264,12 +30264,12 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,09%</t>
         </is>
       </c>
     </row>
